--- a/output/data.xlsx
+++ b/output/data.xlsx
@@ -425,146 +425,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A20"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Substance.chemical_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>ENDPOINT_STUDY_RECORD.RepeatedDoseToxicityOral.materials_and_methods.administration_exposure.route_of_administration.value</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>ENDPOINT_STUDY_RECORD.RepeatedDoseToxicityOral.materials_and_methods.test_animals.species.value</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>7783186</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
-          <t>oral: gavage</t>
+          <t>Not Specified</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
-          <t>oral: feed</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>oral, oral: gavage</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>oral: capsule</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>oral: feed</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>oral, oral: feed</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>oral, oral: gavage</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>oral: feed</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>oral: gavage</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>oral: drinking water</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>oral, oral: gavage</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>oral: gavage</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>oral: capsule</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>oral: gavage</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>oral</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>oral: gavage</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Oral gavage</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>oral: gavage</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>oral, oral: gavage</t>
+          <t>rat</t>
         </is>
       </c>
     </row>
